--- a/docs/structured-protocol/20261014/evidence/protocol.xlsx
+++ b/docs/structured-protocol/20261014/evidence/protocol.xlsx
@@ -73,7 +73,7 @@
     <t>consumptionRules</t>
   </si>
   <si>
-    <t>SYN-79b5ab5c-dbd4-464b-a250-d996a01b0b48</t>
+    <t>SYN-88d664d2-3767-48f0-a72d-454ea4e871cc</t>
   </si>
   <si>
     <t>350／600 µL 合成规程</t>

--- a/docs/structured-protocol/20261014/evidence/protocol.xlsx
+++ b/docs/structured-protocol/20261014/evidence/protocol.xlsx
@@ -73,7 +73,7 @@
     <t>consumptionRules</t>
   </si>
   <si>
-    <t>SYN-88d664d2-3767-48f0-a72d-454ea4e871cc</t>
+    <t>SYN-a6dfc410-c299-44fc-b93b-652f764e1054</t>
   </si>
   <si>
     <t>350／600 µL 合成规程</t>
